--- a/test_human/21_The_Agent_Competency/_fixtures/reconciliation/vendor_statement.xlsx
+++ b/test_human/21_The_Agent_Competency/_fixtures/reconciliation/vendor_statement.xlsx
@@ -449,7 +449,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>As of 2026-08-09   |   Amounts they show as outstanding</t>
+          <t>As of 2026-08-20   |   Amounts they show as outstanding</t>
         </is>
       </c>
     </row>
